--- a/config/motor.xlsx
+++ b/config/motor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1076F5D7-A096-4115-BB8B-A9DF40FBBAD0}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD9D7E5-E683-4A7B-8EFA-217BA9D3B369}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -1879,7 +1879,7 @@
         <v>107</v>
       </c>
       <c r="F2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
@@ -3305,7 +3305,7 @@
         <v>48</v>
       </c>
       <c r="F29" s="6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>16</v>
@@ -3654,7 +3654,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" s="29" t="s">
         <v>16</v>
@@ -3677,7 +3677,7 @@
         <v>48</v>
       </c>
       <c r="F4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>16</v>

--- a/config/motor.xlsx
+++ b/config/motor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD9D7E5-E683-4A7B-8EFA-217BA9D3B369}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0642A4A3-DE73-4A13-9605-C3BE496B6438}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="4056" yWindow="3288" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
   <si>
     <t>#</t>
   </si>
@@ -780,6 +780,24 @@
   </si>
   <si>
     <t>valPat</t>
+  </si>
+  <si>
+    <t>Window Length</t>
+  </si>
+  <si>
+    <t>Length of the input window for sequence to point learning. The input dimension of the model is (FxWxNt) where F are the features, W is the window, and Nt are the number of samples.</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Window Strides</t>
+  </si>
+  <si>
+    <t>The strides describe the overab from one window to the next window.</t>
+  </si>
+  <si>
+    <t>stride</t>
   </si>
 </sst>
 </file>
@@ -2636,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3472,55 +3490,83 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="6">
+        <v>50</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="6">
+        <v>1</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B39" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D39" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E39" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F39" s="10">
         <v>25</v>
       </c>
-      <c r="G37" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="31"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="29"/>
+      <c r="G39" s="30" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="29"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
@@ -3531,12 +3577,30 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="29"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="29"/>
+    </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F41" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
@@ -3566,7 +3630,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F37 F32 F34:F35" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F39 F32 F34:F35 F37" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
